--- a/artfynd/A 15256-2026 artfynd.xlsx
+++ b/artfynd/A 15256-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127796831</v>
       </c>
       <c r="B2" t="n">
-        <v>78749</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127796848</v>
+        <v>128484929</v>
       </c>
       <c r="B3" t="n">
-        <v>79673</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467684</v>
+        <v>467411</v>
       </c>
       <c r="R3" t="n">
-        <v>6867470</v>
+        <v>6867573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127796935</v>
+        <v>128485709</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467564</v>
+        <v>467387</v>
       </c>
       <c r="R4" t="n">
-        <v>6867390</v>
+        <v>6867345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127797054</v>
+        <v>128518707</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467476</v>
+        <v>467737</v>
       </c>
       <c r="R5" t="n">
-        <v>6867493</v>
+        <v>6867274</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127797105</v>
+        <v>128518797</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467441</v>
+        <v>467714</v>
       </c>
       <c r="R6" t="n">
-        <v>6867484</v>
+        <v>6867283</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1138,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127796731</v>
+        <v>128518939</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467761</v>
+        <v>467658</v>
       </c>
       <c r="R7" t="n">
-        <v>6867399</v>
+        <v>6867254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127797553</v>
+        <v>128518668</v>
       </c>
       <c r="B8" t="n">
-        <v>78841</v>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
+          <t>Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467419</v>
+        <v>467827</v>
       </c>
       <c r="R8" t="n">
-        <v>6867271</v>
+        <v>6867330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127797231</v>
+        <v>127796731</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467417</v>
+        <v>467761</v>
       </c>
       <c r="R9" t="n">
-        <v>6867415</v>
+        <v>6867399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128486152</v>
+        <v>128486009</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,43 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467326</v>
+        <v>467344</v>
       </c>
       <c r="R10" t="n">
-        <v>6867404</v>
+        <v>6867344</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484618</v>
+        <v>128486029</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467370</v>
+        <v>467343</v>
       </c>
       <c r="R11" t="n">
-        <v>6867567</v>
+        <v>6867360</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484488</v>
+        <v>128486103</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467296</v>
+        <v>467340</v>
       </c>
       <c r="R12" t="n">
-        <v>6867571</v>
+        <v>6867371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128485668</v>
+        <v>128486130</v>
       </c>
       <c r="B13" t="n">
-        <v>98646</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,43 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467380</v>
+        <v>467340</v>
       </c>
       <c r="R13" t="n">
-        <v>6867346</v>
+        <v>6867393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484498</v>
+        <v>128484488</v>
       </c>
       <c r="B14" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467297</v>
+        <v>467296</v>
       </c>
       <c r="R14" t="n">
-        <v>6867574</v>
+        <v>6867571</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485709</v>
+        <v>128484618</v>
       </c>
       <c r="B15" t="n">
-        <v>78695</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467387</v>
+        <v>467370</v>
       </c>
       <c r="R15" t="n">
-        <v>6867345</v>
+        <v>6867567</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2066,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486130</v>
+        <v>127796935</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lassbodberget, Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467340</v>
+        <v>467564</v>
       </c>
       <c r="R16" t="n">
-        <v>6867393</v>
+        <v>6867390</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2131,12 +2098,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2163,45 +2135,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128485715</v>
+        <v>127797054</v>
       </c>
       <c r="B17" t="n">
-        <v>98646</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lassbodberget, Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467371</v>
+        <v>467476</v>
       </c>
       <c r="R17" t="n">
-        <v>6867346</v>
+        <v>6867493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,12 +2200,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2260,54 +2237,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128484758</v>
+        <v>127797231</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lassbodberget, Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467386</v>
+        <v>467417</v>
       </c>
       <c r="R18" t="n">
-        <v>6867534</v>
+        <v>6867415</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,12 +2302,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2366,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128486214</v>
+        <v>128519428</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2401,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467336</v>
+        <v>467584</v>
       </c>
       <c r="R19" t="n">
-        <v>6867418</v>
+        <v>6867351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,12 +2404,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2463,57 +2441,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128485871</v>
+        <v>128518723</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467353</v>
+        <v>467737</v>
       </c>
       <c r="R20" t="n">
-        <v>6867298</v>
+        <v>6867274</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2537,12 +2506,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Läten noterade.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2569,45 +2543,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128486103</v>
+        <v>128484700</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467340</v>
+        <v>467385</v>
       </c>
       <c r="R21" t="n">
-        <v>6867371</v>
+        <v>6867556</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,45 +2649,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484929</v>
+        <v>128484758</v>
       </c>
       <c r="B22" t="n">
-        <v>78695</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467411</v>
+        <v>467386</v>
       </c>
       <c r="R22" t="n">
-        <v>6867573</v>
+        <v>6867534</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,42 +2755,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486029</v>
+        <v>128485651</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467343</v>
+        <v>467382</v>
       </c>
       <c r="R23" t="n">
         <v>6867360</v>
@@ -2860,45 +2861,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128484624</v>
+        <v>128485668</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467372</v>
+        <v>467380</v>
       </c>
       <c r="R24" t="n">
-        <v>6867560</v>
+        <v>6867346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,10 +2967,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128485651</v>
+        <v>128485715</v>
       </c>
       <c r="B25" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,26 +2995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467382</v>
+        <v>467371</v>
       </c>
       <c r="R25" t="n">
-        <v>6867360</v>
+        <v>6867346</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,10 +3064,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128486074</v>
+        <v>128485750</v>
       </c>
       <c r="B26" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3091,17 +3092,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467329</v>
+        <v>467374</v>
       </c>
       <c r="R26" t="n">
-        <v>6867367</v>
+        <v>6867328</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128485883</v>
+        <v>128485871</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3188,17 +3198,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467348</v>
+        <v>467353</v>
       </c>
       <c r="R27" t="n">
-        <v>6867319</v>
+        <v>6867298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3257,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B28" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3285,26 +3304,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R28" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,32 +3373,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128486009</v>
+        <v>128486074</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3398,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467344</v>
+        <v>467329</v>
       </c>
       <c r="R29" t="n">
-        <v>6867344</v>
+        <v>6867367</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3460,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128485750</v>
+        <v>128486152</v>
       </c>
       <c r="B30" t="n">
-        <v>98646</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3490,7 +3500,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3504,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467374</v>
+        <v>467326</v>
       </c>
       <c r="R30" t="n">
-        <v>6867328</v>
+        <v>6867404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,10 +3576,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128518797</v>
+        <v>127797105</v>
       </c>
       <c r="B31" t="n">
-        <v>78700</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,37 +3587,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lassbodberget, Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467714</v>
+        <v>467441</v>
       </c>
       <c r="R31" t="n">
-        <v>6867283</v>
+        <v>6867484</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,12 +3641,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3663,10 +3673,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128518939</v>
+        <v>127797553</v>
       </c>
       <c r="B32" t="n">
-        <v>78700</v>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,34 +3684,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lassbodberget, Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467658</v>
+        <v>467419</v>
       </c>
       <c r="R32" t="n">
-        <v>6867254</v>
+        <v>6867271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,12 +3738,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3760,10 +3770,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128519134</v>
+        <v>128484498</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3795,10 +3805,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467662</v>
+        <v>467297</v>
       </c>
       <c r="R33" t="n">
-        <v>6867285</v>
+        <v>6867574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,12 +3835,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3857,10 +3867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128519551</v>
+        <v>128484624</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3868,21 +3878,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3892,13 +3902,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467578</v>
+        <v>467372</v>
       </c>
       <c r="R34" t="n">
-        <v>6867346</v>
+        <v>6867560</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3922,12 +3932,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3954,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128518723</v>
+        <v>128486214</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3965,21 +3975,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3989,13 +3999,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467737</v>
+        <v>467336</v>
       </c>
       <c r="R35" t="n">
-        <v>6867274</v>
+        <v>6867418</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4019,17 +4029,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Läten noterade.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4056,10 +4061,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128518668</v>
+        <v>128519134</v>
       </c>
       <c r="B36" t="n">
-        <v>79113</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4067,34 +4072,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lassbodberget, Hjd</t>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467827</v>
+        <v>467662</v>
       </c>
       <c r="R36" t="n">
-        <v>6867330</v>
+        <v>6867285</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4156,7 +4161,7 @@
         <v>128520449</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,10 +4255,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128518707</v>
+        <v>127796848</v>
       </c>
       <c r="B38" t="n">
-        <v>78700</v>
+        <v>79917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4261,37 +4266,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lassbodberget, Hjd</t>
+          <t>Lassbodsjön, Lassbodsjön, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467737</v>
+        <v>467684</v>
       </c>
       <c r="R38" t="n">
-        <v>6867274</v>
+        <v>6867470</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4315,12 +4320,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4350,7 +4355,7 @@
         <v>128518947</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4447,7 +4452,7 @@
         <v>128519150</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>79917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,10 +4546,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128519428</v>
+        <v>128519551</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>79917</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4552,21 +4557,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4576,13 +4581,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467584</v>
+        <v>467578</v>
       </c>
       <c r="R41" t="n">
-        <v>6867351</v>
+        <v>6867346</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4612,11 +4617,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 15256-2026 artfynd.xlsx
+++ b/artfynd/A 15256-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484929</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518707</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518939</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518668</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486029</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486103</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484488</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484618</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796935</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127797054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127797231</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518723</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484700</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2752,6 +2857,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484758</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485651</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2964,6 +3079,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485668</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3061,6 +3181,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485715</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3167,6 +3292,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485750</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3273,6 +3403,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485871</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3370,6 +3505,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485883</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3467,6 +3607,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486074</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486152</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127797105</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3767,6 +3922,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127797553</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3864,6 +4024,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484498</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3961,6 +4126,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484624</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4058,6 +4228,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486214</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4155,6 +4330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519134</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4252,6 +4432,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128520449</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4349,6 +4534,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796848</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4446,6 +4636,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518947</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4543,6 +4738,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519150</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4640,8 +4840,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>